--- a/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:16:08+00:00</t>
+    <t>2026-09-29T14:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T14:28:05+00:00</t>
+    <t>2026-09-30T20:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/main/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:36:50+00:00</t>
+    <t>2026-10-01T12:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
 </t>
   </si>
   <si>
-    <t>Persistent identifier for the bundle</t>
+    <t>Identifiant unique du document</t>
   </si>
   <si>
     <t>A persistent identifier for the bundle that won't change as a bundle is copied from server to server.</t>
